--- a/output/3_月度对比汇总.xlsx
+++ b/output/3_月度对比汇总.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Token使用人数" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="AI-IDE订阅人数" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="AI-IDE满意度" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="场景发布" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,11 +444,6 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>环比增长</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
           <t>环比增长率(%)</t>
         </is>
       </c>
@@ -468,76 +464,64 @@
         <v>5983357737</v>
       </c>
       <c r="E2" t="n">
-        <v>3650167876</v>
-      </c>
-      <c r="F2" t="n">
         <v>256.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>质量效能组</t>
+          <t>Coohom技术与数据开发组</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>125</v>
+        <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>826811623</v>
+        <v>532432621</v>
       </c>
       <c r="D3" t="n">
-        <v>1962034046</v>
+        <v>1267022740</v>
       </c>
       <c r="E3" t="n">
-        <v>1135222423</v>
-      </c>
-      <c r="F3" t="n">
-        <v>237.3</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Coohom技术与数据开发组</t>
+          <t>DeepCAD</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>532432621</v>
+        <v>319002571</v>
       </c>
       <c r="D4" t="n">
-        <v>1267022740</v>
+        <v>376617443</v>
       </c>
       <c r="E4" t="n">
-        <v>734590119</v>
-      </c>
-      <c r="F4" t="n">
-        <v>238</v>
+        <v>118.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>工具后端部</t>
+          <t>KooLab组</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C5" t="n">
-        <v>264906524</v>
+        <v>15049812</v>
       </c>
       <c r="D5" t="n">
-        <v>1115538484</v>
+        <v>94178934</v>
       </c>
       <c r="E5" t="n">
-        <v>850631960</v>
-      </c>
-      <c r="F5" t="n">
-        <v>421.1</v>
+        <v>625.8</v>
       </c>
     </row>
     <row r="6">
@@ -556,32 +540,26 @@
         <v>763445491</v>
       </c>
       <c r="E6" t="n">
-        <v>568049852</v>
-      </c>
-      <c r="F6" t="n">
         <v>390.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DeepCAD</t>
+          <t>工具后端部</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="C7" t="n">
-        <v>319002571</v>
+        <v>264906524</v>
       </c>
       <c r="D7" t="n">
-        <v>376617443</v>
+        <v>1115538484</v>
       </c>
       <c r="E7" t="n">
-        <v>57614872</v>
-      </c>
-      <c r="F7" t="n">
-        <v>118.1</v>
+        <v>421.1</v>
       </c>
     </row>
     <row r="8">
@@ -600,9 +578,6 @@
         <v>230084469</v>
       </c>
       <c r="E8" t="n">
-        <v>214278181</v>
-      </c>
-      <c r="F8" t="n">
         <v>1455.7</v>
       </c>
     </row>
@@ -622,32 +597,26 @@
         <v>174436130</v>
       </c>
       <c r="E9" t="n">
-        <v>10651347</v>
-      </c>
-      <c r="F9" t="n">
         <v>106.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KooLab组</t>
+          <t>质量效能组</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="C10" t="n">
-        <v>15049812</v>
+        <v>826811623</v>
       </c>
       <c r="D10" t="n">
-        <v>94178934</v>
+        <v>1962034046</v>
       </c>
       <c r="E10" t="n">
-        <v>79129122</v>
-      </c>
-      <c r="F10" t="n">
-        <v>625.8</v>
+        <v>237.3</v>
       </c>
     </row>
   </sheetData>
@@ -661,7 +630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,11 +656,6 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>环比增长($)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
           <t>环比增长率(%)</t>
         </is>
       </c>
@@ -712,9 +676,6 @@
         <v>1142.88</v>
       </c>
       <c r="E2" t="n">
-        <v>628.16</v>
-      </c>
-      <c r="F2" t="n">
         <v>222</v>
       </c>
     </row>
@@ -734,54 +695,45 @@
         <v>315.05</v>
       </c>
       <c r="E3" t="n">
-        <v>181.82</v>
-      </c>
-      <c r="F3" t="n">
         <v>236.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>质量效能组</t>
+          <t>DeepCAD</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>125</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>155.98</v>
+        <v>59.64</v>
       </c>
       <c r="D4" t="n">
-        <v>308.03</v>
+        <v>59.76</v>
       </c>
       <c r="E4" t="n">
-        <v>152.05</v>
-      </c>
-      <c r="F4" t="n">
-        <v>197.5</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>工具后端部</t>
+          <t>KooLab组</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C5" t="n">
-        <v>60.81</v>
+        <v>1.05</v>
       </c>
       <c r="D5" t="n">
-        <v>185.6</v>
+        <v>34.13</v>
       </c>
       <c r="E5" t="n">
-        <v>124.79</v>
-      </c>
-      <c r="F5" t="n">
-        <v>305.2</v>
+        <v>3250.5</v>
       </c>
     </row>
     <row r="6">
@@ -800,98 +752,83 @@
         <v>144.91</v>
       </c>
       <c r="E6" t="n">
-        <v>92.95</v>
-      </c>
-      <c r="F6" t="n">
         <v>278.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DeepCAD</t>
+          <t>工具后端部</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="C7" t="n">
-        <v>59.64</v>
+        <v>60.81</v>
       </c>
       <c r="D7" t="n">
-        <v>59.76</v>
+        <v>185.6</v>
       </c>
       <c r="E7" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="F7" t="n">
-        <v>100.2</v>
+        <v>305.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>算力中心</t>
+          <t>渲染组</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C8" t="n">
-        <v>48.16</v>
+        <v>3.88</v>
       </c>
       <c r="D8" t="n">
-        <v>51.71</v>
+        <v>43.68</v>
       </c>
       <c r="E8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="F8" t="n">
-        <v>107.4</v>
+        <v>1125.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>渲染组</t>
+          <t>算力中心</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>3.88</v>
+        <v>48.16</v>
       </c>
       <c r="D9" t="n">
-        <v>43.68</v>
+        <v>51.71</v>
       </c>
       <c r="E9" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1125.8</v>
+        <v>107.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KooLab组</t>
+          <t>质量效能组</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="C10" t="n">
-        <v>1.05</v>
+        <v>155.98</v>
       </c>
       <c r="D10" t="n">
-        <v>34.13</v>
+        <v>308.03</v>
       </c>
       <c r="E10" t="n">
-        <v>33.08</v>
-      </c>
-      <c r="F10" t="n">
-        <v>3250.5</v>
+        <v>197.5</v>
       </c>
     </row>
   </sheetData>
@@ -905,7 +842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -931,11 +868,6 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>环比增长</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
           <t>环比增长率(%)</t>
         </is>
       </c>
@@ -956,76 +888,64 @@
         <v>170</v>
       </c>
       <c r="E2" t="n">
-        <v>46</v>
-      </c>
-      <c r="F2" t="n">
         <v>137.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>质量效能组</t>
+          <t>Coohom技术与数据开发组</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>125</v>
+        <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
-      </c>
-      <c r="F3" t="n">
-        <v>187.5</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>工具后端部</t>
+          <t>DeepCAD</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F4" t="n">
-        <v>130.8</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Coohom技术与数据开发组</t>
+          <t>KooLab组</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>120</v>
+        <v>133.3</v>
       </c>
     </row>
     <row r="6">
@@ -1044,32 +964,26 @@
         <v>30</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="n">
         <v>107.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>算力中心</t>
+          <t>工具后端部</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>122.2</v>
+        <v>130.8</v>
       </c>
     </row>
     <row r="8">
@@ -1088,54 +1002,45 @@
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" t="n">
         <v>200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DeepCAD</t>
+          <t>算力中心</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>150</v>
+        <v>122.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KooLab组</t>
+          <t>质量效能组</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>133.3</v>
+        <v>187.5</v>
       </c>
     </row>
   </sheetData>
@@ -1149,7 +1054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1175,11 +1080,6 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>环比增长</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
           <t>环比增长率(%)</t>
         </is>
       </c>
@@ -1194,16 +1094,13 @@
         <v>576</v>
       </c>
       <c r="C2" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-12</v>
-      </c>
-      <c r="F2" t="n">
-        <v>73.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1216,15 +1113,12 @@
         <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1246,18 +1140,15 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>工具前端部</t>
+          <t>KooLab组</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -1266,31 +1157,25 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KooLab组</t>
+          <t>工具前端部</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1304,15 +1189,12 @@
         <v>62</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1326,15 +1208,12 @@
         <v>34</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1356,9 +1235,6 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1370,15 +1246,12 @@
         <v>125</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1393,7 +1266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1419,11 +1292,6 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>满意度变化</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
           <t>满意度变化率(%)</t>
         </is>
       </c>
@@ -1438,16 +1306,13 @@
         <v>576</v>
       </c>
       <c r="C2" t="n">
-        <v>813676.5</v>
+        <v>4.2</v>
       </c>
       <c r="D2" t="n">
-        <v>604740.9</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-208935.6</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-25.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1460,16 +1325,13 @@
         <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-100</v>
       </c>
     </row>
     <row r="4">
@@ -1490,18 +1352,15 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
-        <v>-100</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>工具前端部</t>
+          <t>KooLab组</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -1511,31 +1370,25 @@
       </c>
       <c r="E5" t="n">
         <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-100</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KooLab组</t>
+          <t>工具前端部</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-100</v>
       </c>
     </row>
     <row r="7">
@@ -1548,16 +1401,13 @@
         <v>62</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-100</v>
       </c>
     </row>
     <row r="8">
@@ -1578,9 +1428,6 @@
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="n">
-        <v>-100</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1600,9 +1447,6 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
-        <v>-100</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1614,7 +1458,7 @@
         <v>125</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -1622,8 +1466,71 @@
       <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" t="n">
-        <v>-100</v>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>人数</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>后端</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>算法</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/output/3_月度对比汇总.xlsx
+++ b/output/3_月度对比汇总.xlsx
@@ -464,7 +464,7 @@
         <v>5983357737</v>
       </c>
       <c r="E2" t="n">
-        <v>256.4</v>
+        <v>156.4</v>
       </c>
     </row>
     <row r="3">
@@ -483,7 +483,7 @@
         <v>1267022740</v>
       </c>
       <c r="E3" t="n">
-        <v>238</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4">
@@ -502,7 +502,7 @@
         <v>376617443</v>
       </c>
       <c r="E4" t="n">
-        <v>118.1</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="5">
@@ -521,7 +521,7 @@
         <v>94178934</v>
       </c>
       <c r="E5" t="n">
-        <v>625.8</v>
+        <v>525.8</v>
       </c>
     </row>
     <row r="6">
@@ -540,7 +540,7 @@
         <v>763445491</v>
       </c>
       <c r="E6" t="n">
-        <v>390.7</v>
+        <v>290.7</v>
       </c>
     </row>
     <row r="7">
@@ -559,7 +559,7 @@
         <v>1115538484</v>
       </c>
       <c r="E7" t="n">
-        <v>421.1</v>
+        <v>321.1</v>
       </c>
     </row>
     <row r="8">
@@ -578,7 +578,7 @@
         <v>230084469</v>
       </c>
       <c r="E8" t="n">
-        <v>1455.7</v>
+        <v>1355.7</v>
       </c>
     </row>
     <row r="9">
@@ -597,7 +597,7 @@
         <v>174436130</v>
       </c>
       <c r="E9" t="n">
-        <v>106.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="10">
@@ -616,7 +616,7 @@
         <v>1962034046</v>
       </c>
       <c r="E10" t="n">
-        <v>237.3</v>
+        <v>137.3</v>
       </c>
     </row>
   </sheetData>
@@ -676,7 +676,7 @@
         <v>1142.88</v>
       </c>
       <c r="E2" t="n">
-        <v>222</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3">
@@ -695,7 +695,7 @@
         <v>315.05</v>
       </c>
       <c r="E3" t="n">
-        <v>236.5</v>
+        <v>136.5</v>
       </c>
     </row>
     <row r="4">
@@ -714,7 +714,7 @@
         <v>59.76</v>
       </c>
       <c r="E4" t="n">
-        <v>100.2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
@@ -733,7 +733,7 @@
         <v>34.13</v>
       </c>
       <c r="E5" t="n">
-        <v>3250.5</v>
+        <v>3150.5</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         <v>144.91</v>
       </c>
       <c r="E6" t="n">
-        <v>278.9</v>
+        <v>178.9</v>
       </c>
     </row>
     <row r="7">
@@ -771,7 +771,7 @@
         <v>185.6</v>
       </c>
       <c r="E7" t="n">
-        <v>305.2</v>
+        <v>205.2</v>
       </c>
     </row>
     <row r="8">
@@ -790,7 +790,7 @@
         <v>43.68</v>
       </c>
       <c r="E8" t="n">
-        <v>1125.8</v>
+        <v>1025.8</v>
       </c>
     </row>
     <row r="9">
@@ -809,7 +809,7 @@
         <v>51.71</v>
       </c>
       <c r="E9" t="n">
-        <v>107.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="10">
@@ -828,7 +828,7 @@
         <v>308.03</v>
       </c>
       <c r="E10" t="n">
-        <v>197.5</v>
+        <v>97.5</v>
       </c>
     </row>
   </sheetData>
@@ -888,7 +888,7 @@
         <v>170</v>
       </c>
       <c r="E2" t="n">
-        <v>137.1</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="3">
@@ -907,7 +907,7 @@
         <v>30</v>
       </c>
       <c r="E3" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -926,7 +926,7 @@
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -945,7 +945,7 @@
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>133.3</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="6">
@@ -964,7 +964,7 @@
         <v>30</v>
       </c>
       <c r="E6" t="n">
-        <v>107.1</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7">
@@ -983,7 +983,7 @@
         <v>34</v>
       </c>
       <c r="E7" t="n">
-        <v>130.8</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="8">
@@ -1002,7 +1002,7 @@
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -1021,7 +1021,7 @@
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>122.2</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="10">
@@ -1040,7 +1040,7 @@
         <v>45</v>
       </c>
       <c r="E10" t="n">
-        <v>187.5</v>
+        <v>87.5</v>
       </c>
     </row>
   </sheetData>
@@ -1100,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="3">
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="4">
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="7">
@@ -1195,7 +1195,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="8">
@@ -1214,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="9">
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
   </sheetData>

--- a/output/3_月度对比汇总.xlsx
+++ b/output/3_月度对比汇总.xlsx
@@ -1094,7 +1094,7 @@
         <v>576</v>
       </c>
       <c r="C2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1246,7 +1246,7 @@
         <v>125</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>125</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>

--- a/output/3_月度对比汇总.xlsx
+++ b/output/3_月度对比汇总.xlsx
@@ -1060,7 +1060,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>部门</t>
+          <t>二级部门</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -1094,13 +1094,13 @@
         <v>576</v>
       </c>
       <c r="C2" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="E2" t="n">
-        <v>-100</v>
+        <v>293.8</v>
       </c>
     </row>
     <row r="3">
@@ -1113,13 +1113,13 @@
         <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1154,10 +1154,10 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -1170,13 +1170,13 @@
         <v>120</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E6" t="n">
-        <v>-100</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="7">
@@ -1189,13 +1189,13 @@
         <v>62</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>-100</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
@@ -1208,13 +1208,13 @@
         <v>34</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>-100</v>
+        <v>-33.3</v>
       </c>
     </row>
     <row r="9">
@@ -1230,10 +1230,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
@@ -1246,13 +1246,13 @@
         <v>125</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>-100</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +1458,7 @@
         <v>125</v>
       </c>
       <c r="C10" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
